--- a/s02/descargables/S02_ALU_03_Matriz_Riesgo_EBR.xlsx
+++ b/s02/descargables/S02_ALU_03_Matriz_Riesgo_EBR.xlsx
@@ -554,7 +554,7 @@
     <t xml:space="preserve">Severidad (ref.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Si una operación con recursos de procedencia ilícita se materializara en la entidad, el impacto sería simultáneo en cuatro planos. LEGAL: las multas del Art. 54 de la Ley van de 200 a 65,000 UMA por Aviso omitido o extemporáneo —entre $23,462 y $7,625,150 al valor vigente de la UMA— y la conducta puede escalar a responsabilidad penal por el Art. 400 Bis del Código Penal Federal para quien intervino a sabiendas. REPUTACIONAL: el negocio depende de la recomendación entre compradores y de la relación con tres desarrolladoras; una nota pública o un requerimiento conocido bastaría para frenar la preventa del desarrollo en curso. DE CONTAGIO: las instituciones financieras con las que se dispersan los recursos aplican sus propias medidas del Art. 115 de la LIC y pueden restringir o cancelar las cuentas de la entidad, lo que detendría la operación aunque no hubiera sanción. OPERATIVO: atender un requerimiento con expedientes incompletos consumiría a la Encargada de Cumplimiento y al área jurídica durante semanas, con el costo de oportunidad correspondiente.</t>
+    <t xml:space="preserve">Si una operación con recursos de procedencia ilícita se materializara en la entidad, el impacto sería simultáneo en cuatro planos. LEGAL: la multa por Aviso omitido es de 10,000 a 65,000 UMA, o del 10 al 100 % del valor del acto cuando sea cuantificable, la que resulte mayor (Art. 53 fr. VI con Art. 54 fr. III de la Ley) —entre $1,173,100 y $7,625,150 al valor vigente de la UMA, y en una operación de este tamaño manda el porcentaje— y la conducta puede escalar a responsabilidad penal por el Art. 400 Bis del Código Penal Federal para quien intervino a sabiendas. REPUTACIONAL: el negocio depende de la recomendación entre compradores y de la relación con tres desarrolladoras; una nota pública o un requerimiento conocido bastaría para frenar la preventa del desarrollo en curso. DE CONTAGIO: las instituciones financieras con las que se dispersan los recursos aplican sus propias medidas del Art. 115 de la LIC y pueden restringir o cancelar las cuentas de la entidad, lo que detendría la operación aunque no hubiera sanción. OPERATIVO: atender un requerimiento con expedientes incompletos consumiría a la Encargada de Cumplimiento y al área jurídica durante semanas, con el costo de oportunidad correspondiente.</t>
   </si>
   <si>
     <t xml:space="preserve">Grave</t>
@@ -855,7 +855,7 @@
     <t xml:space="preserve">Cap. XIV, Arts. 42 a 51</t>
   </si>
   <si>
-    <t xml:space="preserve">Programa de revisión anual y designación de quien emite el dictamen: área interna si tu riesgo es bajo o medio; auditor externo certificado por la UIF si es alto (ver A6).</t>
+    <t xml:space="preserve">Programa de revisión anual y designación de quien emite el dictamen: puede ser el área interna si tu riesgo es bajo o medio (Art. 44); auditor externo certificado por la UIF si es alto, o si así lo eliges (Art. 45). Ver A6.</t>
   </si>
   <si>
     <t xml:space="preserve">Manual, numeral 10.1</t>
@@ -942,7 +942,7 @@
     <t xml:space="preserve">Cómo se calcula: Efectividad = suma de los porcentajes ÷ obligaciones exigibles. El denominador es fijo (14) y solo baja cuando una obligación es «No aplica». Por eso registrar menos controles ya NO mejora el resultado: lo empeora.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sólo las fracciones V, VIII y X admiten «No aplica», y de forma condicionada: V para quien opera exclusivamente con Clientes ocasionales sin Relación de Negocios; VIII para las fracciones cuyo umbral no admite acumulación; X para la persona física que realiza la Actividad Vulnerable sin estructura, porque el Art. 20 de la Ley ata la designación a las personas morales. Las otras once no admiten exclusión.</t>
+    <t xml:space="preserve">El Art. 37 Bis 2 no enlista fracciones: exenta cualquier contenido del Manual referido a actos u operaciones que se determine no realizar, con constancia en el propio Manual. Que en esta matriz sólo se habilite «No aplica» en las fracciones V, VIII y X es criterio de la herramienta, y de forma condicionada: V para quien opera exclusivamente con Clientes ocasionales sin Relación de Negocios; VIII para las fracciones cuyo umbral no admite acumulación; X para la persona física que realiza la Actividad Vulnerable sin estructura, porque el Art. 20 de la Ley ata la designación a las personas morales. Las otras once no admiten exclusión.</t>
   </si>
   <si>
     <t xml:space="preserve">El Art. 48 fr. V exige que el auditor verifique que la exclusión no actualice un incumplimiento y que sea consistente con el análisis de Riesgos. Por eso la justificación pide el numeral del Manual donde consta la exención, no un texto libre.</t>
@@ -1377,10 +1377,10 @@
     <t xml:space="preserve">Bitácora del sistema con dictamen firmado por alerta.</t>
   </si>
   <si>
-    <t xml:space="preserve">La fracción XII quedó en «Cumple parcialmente»: hay programa de auditoría aprobado pero el primer dictamen aún no se emite.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contratar la revisión y emitir el primer dictamen. Con riesgo bajo o medio puede practicarla el área de auditoría interna conforme al Art. 44 de las Reglas.</t>
+    <t xml:space="preserve">La fracción XII quedó en «Cumple parcialmente»: hay programa de auditoría aprobado pero falta designar y preparar al área que emitirá el dictamen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparar el área de auditoría y designar a quien emitirá el dictamen. Con riesgo bajo o medio puede practicarla el área de auditoría interna (Art. 44); con riesgo alto, o si así se elige, va persona auditora externa independiente (Art. 45). El primer periodo de revisión corre del 1 de enero al 31 de diciembre de 2028 (Transitorio Octavo) y el dictamen se entrega a más tardar el último día hábil de marzo de 2029 (Art. 50).</t>
   </si>
   <si>
     <t xml:space="preserve">Órgano de administración</t>
@@ -1392,7 +1392,7 @@
     <t xml:space="preserve">No iniciada</t>
   </si>
   <si>
-    <t xml:space="preserve">Dictamen de auditoría del ejercicio y acta de designación de quien lo emite.</t>
+    <t xml:space="preserve">Programa anual de auditoría y acta de designación de quien emitirá el dictamen; el dictamen del ejercicio 2028 se entrega en marzo de 2029.</t>
   </si>
   <si>
     <t xml:space="preserve">El indicador 13, Beneficiario Controlador, pesa 0.18 dentro del elemento 2 y el régimen cambia: a partir del 30 de noviembre de 2026 desaparece la constancia declarativa en persona moral y fideicomiso, y hay que identificarlo.</t>
@@ -1404,7 +1404,7 @@
     <t xml:space="preserve">Expedientes con Beneficiario Controlador identificado y formato nuevo liberado.</t>
   </si>
   <si>
-    <t xml:space="preserve">El compromiso debe indicar al menos el año y el mes (Art. 10 Septies 2, fr. IV). Un plan sin fecha no acredita mitigación: acredita intención.</t>
+    <t xml:space="preserve">El Art. 10 Septies 2, último párrafo, pide indicar al menos el año y mes EN QUE SE OBTUVIERON LOS RESULTADOS de la implementación: ése ancla el plazo de doce meses. La fecha comprometida de la acción es buena práctica de esta matriz. Un plan sin fecha no acredita mitigación: acredita intención.</t>
   </si>
   <si>
     <t xml:space="preserve">A9 · CONSTANCIA DE LA EVALUACIÓN, FUENTES Y CONSERVACIÓN</t>
@@ -1857,7 +1857,7 @@
     <t xml:space="preserve">No es Persona Políticamente Expuesta</t>
   </si>
   <si>
-    <t xml:space="preserve">Anexo 10 · RCG 23 Bis 3 y 23 Bis 4</t>
+    <t xml:space="preserve">Declaración del Cliente y consulta en Consulta PEP 2.0 · RCG 23 Quáter 1 · RCG 23 Bis 3 y 23 Bis 4</t>
   </si>
   <si>
     <t xml:space="preserve">PEP nacional, comportamiento congruente con ingresos y funciones</t>
@@ -2379,7 +2379,7 @@
     <t xml:space="preserve">Cambio en la condición de Persona Políticamente Expuesta</t>
   </si>
   <si>
-    <t xml:space="preserve">RCG 23 Quáter · Anexo 10</t>
+    <t xml:space="preserve">RCG 23 Quáter · 23 Quáter 1 (Consulta PEP 2.0)</t>
   </si>
   <si>
     <t xml:space="preserve">Cambio significativo en la actividad, el giro o la fuente de los ingresos</t>
@@ -9546,7 +9546,7 @@
     </row>
     <row r="47" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="D47" s="53" t="str">
-        <f aca="false">IF($F$46="","Falta registrar el año y el mes en que se modificarán las políticas conforme a los resultados (Art. 10 Septies 2, último párrafo).","Compromiso registrado. Los dos plazos corren en paralelo: revisar la evaluación y modificar las políticas son obligaciones distintas.")</f>
+        <f aca="false">IF($F$46="","Falta registrar el año y el mes. Ojo: el Art. 10 Septies 2, último párrafo, pide el año y mes EN QUE SE OBTUVIERON LOS RESULTADOS de la implementación, que es el que ancla el plazo de doce meses.","Compromiso registrado. Los dos plazos corren en paralelo: revisar la evaluación y modificar las políticas son obligaciones distintas.")</f>
         <v>Compromiso registrado. Los dos plazos corren en paralelo: revisar la evaluación y modificar las políticas son obligaciones distintas.</v>
       </c>
       <c r="E47" s="53"/>
